--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -461,14 +461,19 @@
     <t>occurenceR5</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationAdministration.occurence%5Bx%5D}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationAdministration.occurence}
 </t>
   </si>
   <si>
     <t>Fréquence d'administration</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationAdministration.occurence[x]` additional types (Timing)</t>
+  </si>
+  <si>
+    <t>Element `MedicationAdministration.occurence[x]` is mapped to FHIR R4 element `MedicationAdministration.effective[x]` as `SourceIsBroaderThanTarget`.
+The mappings for `MedicationAdministration.occurence[x]` do not cover the following types: Timing.
+The target context `MedicationAdministration.effective[x]` is a choice-type element and cannot directly hold extensions. The context is moved up to parent element `MedicationAdministration`.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -524,7 +529,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationAdministration.occurence[x]</t>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationAdministration.occurence</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -540,26 +545,13 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>Specific date/time or interval of time during which the administration took place (or did not take place)</t>
+  </si>
+  <si>
+    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.extension:occurenceR5.value[x]:valueTiming</t>
-  </si>
-  <si>
-    <t>valueTiming</t>
   </si>
   <si>
     <t>MedicationAdministration.modifierExtension</t>
@@ -1214,6 +1206,13 @@
   </si>
   <si>
     <t>If the rate changes over time, and you want to capture this in MedicationAdministration, then each change should be captured as a distinct MedicationAdministration, with a specific MedicationAdministration.dosage.rate, and the date time when the rate change occurred. Typically, the MedicationAdministration.dosage.rate element is not used to convey an average rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>.rateQuantity</t>
@@ -1581,10 +1580,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.08984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.1484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.1796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.11328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2717,7 +2716,9 @@
       <c r="M10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2775,7 +2776,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2784,7 +2785,7 @@
         <v>78</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>78</v>
@@ -2798,10 +2799,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2824,13 +2825,13 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2881,7 +2882,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2899,7 +2900,7 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
@@ -2913,10 +2914,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2987,7 +2988,7 @@
         <v>136</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>78</v>
@@ -2996,7 +2997,7 @@
         <v>137</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3028,10 +3029,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3057,13 +3058,13 @@
         <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3071,7 +3072,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>78</v>
@@ -3113,7 +3114,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>88</v>
@@ -3145,10 +3146,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3171,13 +3172,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3216,17 +3217,19 @@
         <v>78</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3258,44 +3261,46 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -3343,19 +3348,19 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -3373,48 +3378,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
       </c>
@@ -3462,7 +3465,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3474,16 +3477,16 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3492,12 +3495,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3505,32 +3508,30 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3579,7 +3580,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3594,13 +3595,13 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3611,10 +3612,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3637,13 +3638,13 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3694,7 +3695,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3709,10 +3710,10 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3724,12 +3725,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3737,30 +3738,32 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3770,7 +3773,7 @@
         <v>78</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>78</v>
@@ -3785,13 +3788,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3809,13 +3812,13 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
@@ -3824,27 +3827,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3852,32 +3855,30 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3887,7 +3888,7 @@
         <v>78</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>78</v>
@@ -3902,13 +3903,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3926,13 +3927,13 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
@@ -3941,27 +3942,27 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3972,10 +3973,10 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>78</v>
@@ -3984,13 +3985,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4017,13 +4018,13 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
@@ -4041,13 +4042,13 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
@@ -4056,16 +4057,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>78</v>
@@ -4073,10 +4074,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4084,7 +4085,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4096,18 +4097,20 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4132,34 +4135,34 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>88</v>
@@ -4171,27 +4174,27 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4205,7 +4208,7 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -4214,17 +4217,15 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4273,7 +4274,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>88</v>
@@ -4288,16 +4289,16 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -4305,10 +4306,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4316,7 +4317,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
@@ -4328,16 +4329,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4388,10 +4389,10 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>88</v>
@@ -4403,16 +4404,16 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>78</v>
@@ -4420,10 +4421,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4434,7 +4435,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4446,13 +4447,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4503,13 +4504,13 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
@@ -4518,27 +4519,27 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4546,28 +4547,28 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4618,13 +4619,13 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
@@ -4633,27 +4634,27 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>262</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4661,13 +4662,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -4676,13 +4677,13 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4733,13 +4734,13 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
@@ -4748,16 +4749,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -4765,10 +4766,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4779,7 +4780,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4788,16 +4789,16 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>150</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>151</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4848,31 +4849,31 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>152</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -4880,21 +4881,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -4906,15 +4907,17 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>149</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4963,25 +4966,25 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5002,7 +5005,7 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>175</v>
+        <v>276</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5015,24 +5018,26 @@
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5080,7 +5085,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5098,7 +5103,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5112,46 +5117,42 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5175,13 +5176,13 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5199,25 +5200,25 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5231,10 +5232,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5242,7 +5243,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
@@ -5254,16 +5255,16 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5290,34 +5291,34 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5329,10 +5330,10 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5346,10 +5347,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5357,10 +5358,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
@@ -5369,16 +5370,16 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5405,13 +5406,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5429,13 +5430,13 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
@@ -5444,27 +5445,27 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5478,7 +5479,7 @@
         <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -5487,15 +5488,17 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>213</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5520,13 +5523,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5544,7 +5547,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5559,27 +5562,27 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>78</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5590,10 +5593,10 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -5602,16 +5605,16 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5661,13 +5664,13 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
@@ -5676,27 +5679,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>312</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5707,7 +5710,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5719,17 +5722,15 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5778,13 +5779,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5793,27 +5794,27 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5824,10 +5825,10 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>78</v>
@@ -5836,13 +5837,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5893,7 +5894,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5908,27 +5909,27 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5942,7 +5943,7 @@
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -5951,13 +5952,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>328</v>
+        <v>264</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6008,25 +6009,25 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>333</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6040,10 +6041,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6066,13 +6067,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>334</v>
+        <v>150</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>335</v>
+        <v>151</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6123,7 +6124,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>333</v>
+        <v>152</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6135,13 +6136,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>336</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>337</v>
+        <v>153</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6155,10 +6156,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6169,7 +6170,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6181,13 +6182,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6226,37 +6227,35 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6270,12 +6269,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6296,13 +6297,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>134</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6341,17 +6342,19 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6360,7 +6363,7 @@
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>139</v>
@@ -6383,16 +6386,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>78</v>
+        <v>276</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6405,22 +6406,26 @@
         <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>342</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>343</v>
+        <v>277</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6468,7 +6473,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6477,7 +6482,7 @@
         <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>139</v>
@@ -6486,7 +6491,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6498,48 +6503,44 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6587,25 +6588,25 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>131</v>
+        <v>346</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6619,10 +6620,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6645,15 +6646,17 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6678,13 +6681,11 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>78</v>
+        <v>351</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6702,7 +6703,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6720,13 +6721,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6734,10 +6735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6760,17 +6761,15 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6795,29 +6794,31 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="Z45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6835,24 +6836,24 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6866,7 +6867,7 @@
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -6875,15 +6876,17 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6908,31 +6911,31 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Z46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6950,24 +6953,24 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6981,7 +6984,7 @@
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
@@ -6990,16 +6993,16 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>213</v>
+        <v>370</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7025,31 +7028,31 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>368</v>
+        <v>78</v>
       </c>
       <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7067,24 +7070,24 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7107,16 +7110,16 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7154,19 +7157,17 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7184,26 +7185,28 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7224,16 +7227,16 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7271,17 +7274,19 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AC49" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7299,13 +7304,13 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7313,13 +7318,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -7341,16 +7346,16 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7400,7 +7405,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7418,28 +7423,26 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7448,10 +7451,10 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
@@ -7460,16 +7463,16 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7519,13 +7522,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -7537,137 +7540,20 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO52">
+  <autoFilter ref="A1:AO51">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7677,7 +7563,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
